--- a/集計くんPro_10/test_data/集計先.xlsx
+++ b/集計くんPro_10/test_data/集計先.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Aggregate_Pro\集計くんPro_10\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A330ED-6097-4C67-9129-BA0DD9227B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B62C58-1F4C-43EF-B14B-C48F13542DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="24885" windowHeight="13485" tabRatio="567" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1365" yWindow="480" windowWidth="27435" windowHeight="14910" tabRatio="567" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="10" r:id="rId1"/>
@@ -2092,29 +2092,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <CategoryTag1 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
-    <TaxCatchAll xmlns="798f16ab-5b94-4383-b991-fd30b24dfbf2" xsi:nil="true"/>
-    <CategoryTag3 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <CategoryTag2 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C263131061AD3445A23C1C5E3C4ABD10" ma:contentTypeVersion="17" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f544a346d9d04f0c64155d0ce45b60a8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xmlns:ns3="798f16ab-5b94-4383-b991-fd30b24dfbf2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f72f337729779afa07cc4012e008c5d" ns2:_="" ns3:_="">
     <xsd:import namespace="ee8c6f52-211c-4a8d-9d5a-5e974d509624"/>
@@ -2403,26 +2380,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E46C992-9825-4B0F-8EDD-CE66246C6EB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ee8c6f52-211c-4a8d-9d5a-5e974d509624"/>
-    <ds:schemaRef ds:uri="798f16ab-5b94-4383-b991-fd30b24dfbf2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14038804-2345-49FB-ABEE-084151129373}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <CategoryTag1 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
+    <TaxCatchAll xmlns="798f16ab-5b94-4383-b991-fd30b24dfbf2" xsi:nil="true"/>
+    <CategoryTag3 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <CategoryTag2 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AAFDD9B-4224-430A-8114-F0E11FEB2823}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2439,4 +2420,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14038804-2345-49FB-ABEE-084151129373}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E46C992-9825-4B0F-8EDD-CE66246C6EB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ee8c6f52-211c-4a8d-9d5a-5e974d509624"/>
+    <ds:schemaRef ds:uri="798f16ab-5b94-4383-b991-fd30b24dfbf2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/集計くんPro_10/test_data/集計先.xlsx
+++ b/集計くんPro_10/test_data/集計先.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Aggregate_Pro\集計くんPro_10\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B62C58-1F4C-43EF-B14B-C48F13542DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BC6216-D648-46F7-8E2C-51AF25532B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="480" windowWidth="27435" windowHeight="14910" tabRatio="567" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1365" yWindow="570" windowWidth="27435" windowHeight="14910" tabRatio="567" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="10" r:id="rId1"/>
@@ -2092,6 +2092,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <CategoryTag1 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
+    <TaxCatchAll xmlns="798f16ab-5b94-4383-b991-fd30b24dfbf2" xsi:nil="true"/>
+    <CategoryTag3 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <CategoryTag2 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C263131061AD3445A23C1C5E3C4ABD10" ma:contentTypeVersion="17" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f544a346d9d04f0c64155d0ce45b60a8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xmlns:ns3="798f16ab-5b94-4383-b991-fd30b24dfbf2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f72f337729779afa07cc4012e008c5d" ns2:_="" ns3:_="">
     <xsd:import namespace="ee8c6f52-211c-4a8d-9d5a-5e974d509624"/>
@@ -2380,30 +2403,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E46C992-9825-4B0F-8EDD-CE66246C6EB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ee8c6f52-211c-4a8d-9d5a-5e974d509624"/>
+    <ds:schemaRef ds:uri="798f16ab-5b94-4383-b991-fd30b24dfbf2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <CategoryTag1 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
-    <TaxCatchAll xmlns="798f16ab-5b94-4383-b991-fd30b24dfbf2" xsi:nil="true"/>
-    <CategoryTag3 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <CategoryTag2 xmlns="ee8c6f52-211c-4a8d-9d5a-5e974d509624" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14038804-2345-49FB-ABEE-084151129373}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AAFDD9B-4224-430A-8114-F0E11FEB2823}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2420,23 +2439,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14038804-2345-49FB-ABEE-084151129373}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E46C992-9825-4B0F-8EDD-CE66246C6EB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ee8c6f52-211c-4a8d-9d5a-5e974d509624"/>
-    <ds:schemaRef ds:uri="798f16ab-5b94-4383-b991-fd30b24dfbf2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>